--- a/data/profit_target/粗利目標.xlsx
+++ b/data/profit_target/粗利目標.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Users\ntmc2025\Desktop\宝のショートカット\70_調査&amp;依頼案件\20250804_粗利目標（小林院長）\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/genie/dev/ai-apps/Dashboard/data/profit_target/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E7EC247-78F5-49D4-9135-247F4931F355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBAC5B25-E212-FE48-821C-4CF35E56F7A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1200" yWindow="2415" windowWidth="27600" windowHeight="13785" xr2:uid="{550DB2E5-88A1-DB4A-A686-6CCA736E9165}"/>
+    <workbookView xWindow="1200" yWindow="2420" windowWidth="27600" windowHeight="13780" xr2:uid="{550DB2E5-88A1-DB4A-A686-6CCA736E9165}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -523,9 +523,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FED16C5-0FF1-DB48-A3CC-8F51D282E1B6}">
   <dimension ref="A1:P26"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="19.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="20"/>
   <cols>
-    <col min="1" max="1" width="22.44140625" customWidth="1"/>
+    <col min="1" max="1" width="22.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -995,7 +995,7 @@
         <v>15</v>
       </c>
       <c r="B22" s="2">
-        <v>50000</v>
+        <v>45000</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>

--- a/data/profit_target/粗利目標.xlsx
+++ b/data/profit_target/粗利目標.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/genie/dev/ai-apps/Dashboard/data/profit_target/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\v221\医事課共有$\○○医事共有フォルダ○○\A.経営企画室\２.経営企画係長\個別対応案件\20260501_目標設定（小林院長）\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBAC5B25-E212-FE48-821C-4CF35E56F7A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85F23137-634B-471F-8775-18FBA9EF22BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1200" yWindow="2420" windowWidth="27600" windowHeight="13780" xr2:uid="{550DB2E5-88A1-DB4A-A686-6CCA736E9165}"/>
+    <workbookView xWindow="7560" yWindow="375" windowWidth="22950" windowHeight="14400" xr2:uid="{550DB2E5-88A1-DB4A-A686-6CCA736E9165}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -523,9 +523,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FED16C5-0FF1-DB48-A3CC-8F51D282E1B6}">
   <dimension ref="A1:P26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="20"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="19.5"/>
   <cols>
-    <col min="1" max="1" width="22.42578125" customWidth="1"/>
+    <col min="1" max="1" width="22.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -555,7 +555,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="2">
-        <v>30000</v>
+        <v>40000</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -577,7 +577,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>17500</v>
+        <v>17000</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -599,7 +599,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>75000</v>
+        <v>90000</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -621,7 +621,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>100000</v>
+        <v>120000</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -643,7 +643,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>18000</v>
+        <v>22000</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -665,7 +665,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>18000</v>
+        <v>19000</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -687,7 +687,7 @@
         <v>22</v>
       </c>
       <c r="B8" s="2">
-        <v>37000</v>
+        <v>50000</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -709,7 +709,7 @@
         <v>21</v>
       </c>
       <c r="B9" s="2">
-        <v>100000</v>
+        <v>110000</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -731,7 +731,7 @@
         <v>6</v>
       </c>
       <c r="B10" s="2">
-        <v>70000</v>
+        <v>71000</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -753,7 +753,7 @@
         <v>23</v>
       </c>
       <c r="B11" s="2">
-        <v>130000</v>
+        <v>150000</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -775,7 +775,7 @@
         <v>25</v>
       </c>
       <c r="B12" s="2">
-        <v>170000</v>
+        <v>180000</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
@@ -797,7 +797,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="2">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -819,7 +819,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="2">
-        <v>45000</v>
+        <v>40000</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -841,7 +841,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="2">
-        <v>180000</v>
+        <v>190000</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
@@ -863,7 +863,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="2">
-        <v>115000</v>
+        <v>130000</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
@@ -885,7 +885,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="2">
-        <v>40000</v>
+        <v>45000</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
@@ -929,7 +929,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="2">
-        <v>120000</v>
+        <v>135000</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
@@ -973,7 +973,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="2">
-        <v>125000</v>
+        <v>130000</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
@@ -1039,7 +1039,7 @@
         <v>17</v>
       </c>
       <c r="B24" s="2">
-        <v>1400</v>
+        <v>1100</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
@@ -1061,7 +1061,7 @@
         <v>18</v>
       </c>
       <c r="B25" s="2">
-        <v>55000</v>
+        <v>52000</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
@@ -1103,5 +1103,6 @@
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/profit_target/粗利目標.xlsx
+++ b/data/profit_target/粗利目標.xlsx
@@ -1,21 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\v221\医事課共有$\○○医事共有フォルダ○○\A.経営企画室\２.経営企画係長\個別対応案件\20260501_目標設定（小林院長）\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/genie/dev/ai-apps/Dashboard/data/profit_target/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85F23137-634B-471F-8775-18FBA9EF22BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{64251BFD-A739-0D44-859E-B0C55C31395C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7560" yWindow="375" windowWidth="22950" windowHeight="14400" xr2:uid="{550DB2E5-88A1-DB4A-A686-6CCA736E9165}"/>
+    <workbookView xWindow="54140" yWindow="3000" windowWidth="22960" windowHeight="14400" xr2:uid="{550DB2E5-88A1-DB4A-A686-6CCA736E9165}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="外来目標" sheetId="3" r:id="rId1"/>
+    <sheet name="入院目標" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -34,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="32">
   <si>
     <t>心臓血管外科</t>
   </si>
@@ -104,14 +106,7 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>腎内科</t>
-  </si>
-  <si>
     <t>一般消化器外科</t>
-  </si>
-  <si>
-    <t>リウマチ膠原病内科</t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>総合内科</t>
@@ -124,12 +119,48 @@
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>消化器内科</t>
+    <rPh sb="3" eb="4">
+      <t>ナイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>循環器内科</t>
+    <rPh sb="3" eb="4">
+      <t>ナイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リウマチ膠原病内科</t>
+  </si>
+  <si>
+    <t>呼吸器内科</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>総合内科</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>腎内科</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>腎内科</t>
+    <rPh sb="0" eb="2">
+      <t>ジンゾウナイブンピツタイシャナイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -147,6 +178,14 @@
     </font>
     <font>
       <sz val="6"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="游ゴシック"/>
       <family val="2"/>
       <charset val="128"/>
@@ -175,7 +214,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -186,6 +225,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="55" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -521,19 +563,241 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FED16C5-0FF1-DB48-A3CC-8F51D282E1B6}">
-  <dimension ref="A1:P26"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="19.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D6A616B-7A0F-EA47-97C3-4656AF5C9C9D}">
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
-    <col min="1" max="1" width="22.44140625" customWidth="1"/>
+    <col min="1" max="1" width="31.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="4">
+        <v>6165</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="4">
+        <v>26138</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="4">
+        <v>28367</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="4">
+        <v>22285</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="4">
+        <v>5514</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="4">
+        <v>20636</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="4">
+        <v>17256</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="4">
+        <v>3023</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="4">
+        <v>3025</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="4">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="4">
+        <v>3367</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="4">
+        <v>9343</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="4">
+        <v>31603</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="4">
+        <v>21810</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" s="4">
+        <v>36146</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="4">
+        <v>16750</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" s="4">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20" s="4">
+        <v>8857</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="4">
+        <v>11374</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" s="4">
+        <v>29360</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23" s="4">
+        <v>4841</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>2</v>
+      </c>
+      <c r="B24" s="4">
+        <v>19862</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>27</v>
+      </c>
+      <c r="B25" s="4">
+        <v>15629</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" s="4">
+        <v>12005</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD1195CC-9795-0540-AA4A-06C273F9FCAA}">
+  <dimension ref="A1:J27"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="20"/>
+  <cols>
+    <col min="1" max="1" width="28.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
@@ -543,19 +807,13 @@
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-    </row>
-    <row r="2" spans="1:16">
-      <c r="A2" s="1" t="s">
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="1">
         <v>0</v>
-      </c>
-      <c r="B2" s="2">
-        <v>40000</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -565,19 +823,13 @@
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-    </row>
-    <row r="3" spans="1:16">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>17000</v>
+        <v>38835.416448205397</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -587,19 +839,13 @@
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
-      <c r="P3" s="2"/>
-    </row>
-    <row r="4" spans="1:16">
-      <c r="A4" s="1" t="s">
-        <v>2</v>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="B4" s="2">
-        <v>90000</v>
+        <v>83861.504340864587</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -609,19 +855,13 @@
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2"/>
-    </row>
-    <row r="5" spans="1:16">
-      <c r="A5" s="1" t="s">
-        <v>3</v>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="B5" s="2">
-        <v>120000</v>
+        <v>101632.79930176456</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -631,19 +871,13 @@
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2"/>
-    </row>
-    <row r="6" spans="1:16">
-      <c r="A6" s="1" t="s">
-        <v>4</v>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="B6" s="2">
-        <v>22000</v>
+        <v>97714.983312441342</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -653,19 +887,13 @@
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2"/>
-    </row>
-    <row r="7" spans="1:16">
-      <c r="A7" s="1" t="s">
-        <v>5</v>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="B7" s="2">
-        <v>19000</v>
+        <v>39485.770004209888</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -675,19 +903,13 @@
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="A8" s="1" t="s">
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" t="s">
         <v>22</v>
       </c>
       <c r="B8" s="2">
-        <v>50000</v>
+        <v>129363.73060512112</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -697,19 +919,13 @@
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
-    </row>
-    <row r="9" spans="1:16">
-      <c r="A9" s="1" t="s">
-        <v>21</v>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="B9" s="2">
-        <v>110000</v>
+        <v>172744.29342072213</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -719,19 +935,13 @@
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
-      <c r="O9" s="2"/>
-      <c r="P9" s="2"/>
-    </row>
-    <row r="10" spans="1:16">
-      <c r="A10" s="1" t="s">
-        <v>6</v>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="2" t="s">
+        <v>1</v>
       </c>
       <c r="B10" s="2">
-        <v>71000</v>
+        <v>13976.590343043159</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -741,19 +951,13 @@
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2"/>
-    </row>
-    <row r="11" spans="1:16">
-      <c r="A11" t="s">
-        <v>23</v>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="B11" s="2">
-        <v>150000</v>
+        <v>41975.481063424639</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -763,19 +967,13 @@
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2"/>
-    </row>
-    <row r="12" spans="1:16">
-      <c r="A12" s="1" t="s">
-        <v>25</v>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="B12" s="2">
-        <v>180000</v>
+        <v>21889.974038224213</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
@@ -785,19 +983,13 @@
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2"/>
-    </row>
-    <row r="13" spans="1:16">
-      <c r="A13" s="1" t="s">
-        <v>7</v>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="2" t="s">
+        <v>0</v>
       </c>
       <c r="B13" s="2">
-        <v>25000</v>
+        <v>36633.438834765046</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -807,19 +999,13 @@
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2"/>
-    </row>
-    <row r="14" spans="1:16">
-      <c r="A14" s="1" t="s">
-        <v>8</v>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="B14" s="2">
-        <v>40000</v>
+        <v>12656.603835214004</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -829,19 +1015,13 @@
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2"/>
-    </row>
-    <row r="15" spans="1:16">
-      <c r="A15" s="1" t="s">
-        <v>9</v>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>190000</v>
+        <v>103397.42737366149</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
@@ -851,19 +1031,13 @@
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
-      <c r="P15" s="2"/>
-    </row>
-    <row r="16" spans="1:16">
-      <c r="A16" s="1" t="s">
-        <v>10</v>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>130000</v>
+        <v>108190.30530782834</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
@@ -873,19 +1047,13 @@
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
-      <c r="P16" s="2"/>
-    </row>
-    <row r="17" spans="1:16">
-      <c r="A17" s="1" t="s">
-        <v>11</v>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="B17" s="2">
-        <v>45000</v>
+        <v>34854.44295131808</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
@@ -895,19 +1063,13 @@
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
-      <c r="P17" s="2"/>
-    </row>
-    <row r="18" spans="1:16">
-      <c r="A18" s="1" t="s">
-        <v>12</v>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="B18" s="2">
-        <v>68000</v>
+        <v>35249.76299714818</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
@@ -917,19 +1079,13 @@
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
-      <c r="P18" s="2"/>
-    </row>
-    <row r="19" spans="1:16">
-      <c r="A19" s="1" t="s">
-        <v>13</v>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="B19" s="2">
-        <v>135000</v>
+        <v>0</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
@@ -939,19 +1095,13 @@
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
-      <c r="M19" s="2"/>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
-      <c r="P19" s="2"/>
-    </row>
-    <row r="20" spans="1:16">
-      <c r="A20" s="1" t="s">
-        <v>24</v>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B20" s="2">
-        <v>40000</v>
+        <v>10143.31379410963</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
@@ -961,19 +1111,13 @@
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
-      <c r="M20" s="2"/>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
-      <c r="P20" s="2"/>
-    </row>
-    <row r="21" spans="1:16">
-      <c r="A21" s="1" t="s">
-        <v>14</v>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="B21" s="2">
-        <v>130000</v>
+        <v>168625.85936489911</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
@@ -983,19 +1127,13 @@
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
-      <c r="M21" s="2"/>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
-      <c r="P21" s="2"/>
-    </row>
-    <row r="22" spans="1:16">
-      <c r="A22" s="1" t="s">
-        <v>15</v>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="B22" s="2">
-        <v>45000</v>
+        <v>38640.284140183823</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
@@ -1005,19 +1143,13 @@
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
-      <c r="M22" s="2"/>
-      <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
-      <c r="P22" s="2"/>
-    </row>
-    <row r="23" spans="1:16">
-      <c r="A23" s="1" t="s">
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B23" s="2">
-        <v>100000</v>
+        <v>95159.131832205341</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
@@ -1027,19 +1159,13 @@
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
-      <c r="M23" s="2"/>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
-      <c r="P23" s="2"/>
-    </row>
-    <row r="24" spans="1:16">
-      <c r="A24" s="1" t="s">
-        <v>17</v>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="2" t="s">
+        <v>2</v>
       </c>
       <c r="B24" s="2">
-        <v>1100</v>
+        <v>70138.441703665987</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
@@ -1049,19 +1175,13 @@
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
-      <c r="M24" s="2"/>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
-      <c r="P24" s="2"/>
-    </row>
-    <row r="25" spans="1:16">
-      <c r="A25" s="1" t="s">
-        <v>18</v>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="B25" s="2">
-        <v>52000</v>
+        <v>24371.251460491028</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
@@ -1071,19 +1191,13 @@
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
-      <c r="L25" s="2"/>
-      <c r="M25" s="2"/>
-      <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
-      <c r="P25" s="2"/>
-    </row>
-    <row r="26" spans="1:16">
-      <c r="A26" s="1" t="s">
-        <v>19</v>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="B26" s="2">
-        <v>45000</v>
+        <v>37995.425269944244</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
@@ -1093,16 +1207,13 @@
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
-      <c r="L26" s="2"/>
-      <c r="M26" s="2"/>
-      <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
-      <c r="P26" s="2"/>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>